--- a/SGC-CKN/Excel/9b426609-bc11-4864-9624-040a9c036d97_Thi_công_cọc_khoan_nhồi__tường_vây_P8-11_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/9b426609-bc11-4864-9624-040a9c036d97_Thi_công_cọc_khoan_nhồi__tường_vây_P8-11_D800_02-04-2026.xlsx
@@ -147,7 +147,7 @@
 02/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">04:10
+    <t xml:space="preserve">03:40
 02/04/2026</t>
   </si>
   <si>
@@ -157,7 +157,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">04:11
+    <t xml:space="preserve">03:41
 02/04/2026</t>
   </si>
   <si>
@@ -213,7 +213,7 @@
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">07:16
+    <t xml:space="preserve">07:06
 02/04/2026</t>
   </si>
   <si>
@@ -269,7 +269,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -352,12 +352,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -368,7 +362,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -417,12 +411,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -448,11 +442,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -548,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -601,17 +590,17 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -658,16 +647,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1291,16 +1277,16 @@
         <v>6.3</v>
       </c>
       <c r="G12" s="9">
-        <v>9.2</v>
+        <v>-8.2</v>
       </c>
       <c r="H12" s="9">
         <v>0.32</v>
       </c>
       <c r="I12" s="9">
-        <v>2.9</v>
+        <v>14.5</v>
       </c>
       <c r="J12" s="8">
-        <v>9.16</v>
+        <v>45.79</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1323,7 +1309,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="12">
-        <v>9.2</v>
+        <v>-8.2</v>
       </c>
       <c r="G13" s="12">
         <v>16.4</v>
@@ -1332,10 +1318,10 @@
         <v>0.87</v>
       </c>
       <c r="I13" s="12">
-        <v>7.2</v>
+        <v>24.6</v>
       </c>
       <c r="J13" s="8">
-        <v>8.31</v>
+        <v>28.38</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1361,53 +1347,53 @@
         <v>16.4</v>
       </c>
       <c r="G14" s="15">
-        <v>21.5</v>
+        <v>-21.5</v>
       </c>
       <c r="H14" s="15">
-        <v>1.15</v>
+        <v>0.65</v>
       </c>
       <c r="I14" s="15">
-        <v>5.1</v>
-      </c>
-      <c r="J14" s="18">
-        <v>4.43</v>
+        <v>37.9</v>
+      </c>
+      <c r="J14" s="8">
+        <v>58.31</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="19">
-        <v>21.5</v>
-      </c>
-      <c r="G15" s="19">
-        <v>26.7</v>
-      </c>
-      <c r="H15" s="19">
-        <v>0.15</v>
-      </c>
-      <c r="I15" s="19">
-        <v>5.2</v>
-      </c>
-      <c r="J15" s="8">
-        <v>34.67</v>
-      </c>
-      <c r="K15" s="20" t="s">
+      <c r="F15" s="18">
+        <v>-21.5</v>
+      </c>
+      <c r="G15" s="18">
+        <v>-24.7</v>
+      </c>
+      <c r="H15" s="18">
+        <v>0.65</v>
+      </c>
+      <c r="I15" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="J15" s="21">
+        <v>4.92</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1428,19 +1414,19 @@
         <v>50</v>
       </c>
       <c r="F16" s="22">
-        <v>26.7</v>
+        <v>-24.7</v>
       </c>
       <c r="G16" s="22">
-        <v>31.9</v>
+        <v>-34.8</v>
       </c>
       <c r="H16" s="22">
         <v>0.65</v>
       </c>
       <c r="I16" s="22">
-        <v>5.2</v>
+        <v>10.1</v>
       </c>
       <c r="J16" s="8">
-        <v>8</v>
+        <v>15.54</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1463,19 +1449,19 @@
         <v>54</v>
       </c>
       <c r="F17" s="25">
-        <v>31.9</v>
+        <v>-34.8</v>
       </c>
       <c r="G17" s="25">
-        <v>37.3</v>
+        <v>-37.3</v>
       </c>
       <c r="H17" s="25">
         <v>0.65</v>
       </c>
       <c r="I17" s="25">
-        <v>5.4</v>
-      </c>
-      <c r="J17" s="8">
-        <v>8.31</v>
+        <v>2.5</v>
+      </c>
+      <c r="J17" s="21">
+        <v>3.85</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1498,7 +1484,7 @@
         <v>58</v>
       </c>
       <c r="F18" s="28">
-        <v>37.3</v>
+        <v>-37.3</v>
       </c>
       <c r="G18" s="28">
         <v>39.5</v>
@@ -1507,10 +1493,10 @@
         <v>0.65</v>
       </c>
       <c r="I18" s="28">
-        <v>2.2</v>
-      </c>
-      <c r="J18" s="18">
-        <v>3.38</v>
+        <v>76.8</v>
+      </c>
+      <c r="J18" s="8">
+        <v>118.15</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1536,16 +1522,16 @@
         <v>39.5</v>
       </c>
       <c r="G19" s="31">
-        <v>43.7</v>
+        <v>-43.7</v>
       </c>
       <c r="H19" s="31">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="I19" s="31">
-        <v>4.2</v>
-      </c>
-      <c r="J19" s="18">
-        <v>3.55</v>
+        <v>83.2</v>
+      </c>
+      <c r="J19" s="8">
+        <v>61.63</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1568,7 +1554,7 @@
         <v>66</v>
       </c>
       <c r="F20" s="34">
-        <v>43.7</v>
+        <v>-43.7</v>
       </c>
       <c r="G20" s="34">
         <v>44.9</v>
@@ -1577,29 +1563,29 @@
         <v>1.28</v>
       </c>
       <c r="I20" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="J20" s="37">
-        <v>0.94</v>
+        <v>88.6</v>
+      </c>
+      <c r="J20" s="8">
+        <v>69.04</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1767,16 +1753,16 @@
         <v>6.3</v>
       </c>
       <c r="F3" s="9">
-        <v>9.2</v>
+        <v>-8.2</v>
       </c>
       <c r="G3" s="9">
         <v>0.32</v>
       </c>
       <c r="H3" s="9">
-        <v>2.9</v>
+        <v>14.5</v>
       </c>
       <c r="I3" s="8">
-        <v>9.16</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1793,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>9.2</v>
+        <v>-8.2</v>
       </c>
       <c r="F4" s="12">
         <v>16.4</v>
@@ -1802,10 +1788,10 @@
         <v>0.87</v>
       </c>
       <c r="H4" s="12">
-        <v>7.2</v>
+        <v>24.6</v>
       </c>
       <c r="I4" s="8">
-        <v>8.31</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1825,45 +1811,45 @@
         <v>16.4</v>
       </c>
       <c r="F5" s="15">
-        <v>21.5</v>
+        <v>-21.5</v>
       </c>
       <c r="G5" s="15">
-        <v>1.15</v>
+        <v>0.65</v>
       </c>
       <c r="H5" s="15">
-        <v>5.1</v>
-      </c>
-      <c r="I5" s="18">
-        <v>4.43</v>
+        <v>37.9</v>
+      </c>
+      <c r="I5" s="8">
+        <v>58.31</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
-        <v>21.5</v>
-      </c>
-      <c r="F6" s="19">
-        <v>26.7</v>
-      </c>
-      <c r="G6" s="19">
-        <v>0.15</v>
-      </c>
-      <c r="H6" s="19">
-        <v>5.2</v>
-      </c>
-      <c r="I6" s="8">
-        <v>34.67</v>
+      <c r="E6" s="18">
+        <v>-21.5</v>
+      </c>
+      <c r="F6" s="18">
+        <v>-24.7</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.65</v>
+      </c>
+      <c r="H6" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="I6" s="21">
+        <v>4.92</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1880,19 +1866,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>26.7</v>
+        <v>-24.7</v>
       </c>
       <c r="F7" s="22">
-        <v>31.9</v>
+        <v>-34.8</v>
       </c>
       <c r="G7" s="22">
         <v>0.65</v>
       </c>
       <c r="H7" s="22">
-        <v>5.2</v>
+        <v>10.1</v>
       </c>
       <c r="I7" s="8">
-        <v>8</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1909,19 +1895,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>31.9</v>
+        <v>-34.8</v>
       </c>
       <c r="F8" s="25">
-        <v>37.3</v>
+        <v>-37.3</v>
       </c>
       <c r="G8" s="25">
         <v>0.65</v>
       </c>
       <c r="H8" s="25">
-        <v>5.4</v>
-      </c>
-      <c r="I8" s="8">
-        <v>8.31</v>
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="21">
+        <v>3.85</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1938,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>37.3</v>
+        <v>-37.3</v>
       </c>
       <c r="F9" s="28">
         <v>39.5</v>
@@ -1947,10 +1933,10 @@
         <v>0.65</v>
       </c>
       <c r="H9" s="28">
-        <v>2.2</v>
-      </c>
-      <c r="I9" s="18">
-        <v>3.38</v>
+        <v>76.8</v>
+      </c>
+      <c r="I9" s="8">
+        <v>118.15</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1970,16 +1956,16 @@
         <v>39.5</v>
       </c>
       <c r="F10" s="31">
-        <v>43.7</v>
+        <v>-43.7</v>
       </c>
       <c r="G10" s="31">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="H10" s="31">
-        <v>4.2</v>
-      </c>
-      <c r="I10" s="18">
-        <v>3.55</v>
+        <v>83.2</v>
+      </c>
+      <c r="I10" s="8">
+        <v>61.63</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1996,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>43.7</v>
+        <v>-43.7</v>
       </c>
       <c r="F11" s="34">
         <v>44.9</v>
@@ -2005,39 +1991,39 @@
         <v>1.28</v>
       </c>
       <c r="H11" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="I11" s="37">
-        <v>0.94</v>
+        <v>88.6</v>
+      </c>
+      <c r="I11" s="8">
+        <v>69.04</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>0</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="39">
         <v>44.9</v>
       </c>
-      <c r="G12" s="40">
-        <v>7.23</v>
-      </c>
-      <c r="H12" s="40">
-        <v>44.9</v>
-      </c>
-      <c r="I12" s="40">
-        <v>6.21</v>
+      <c r="G12" s="39">
+        <v>7.4</v>
+      </c>
+      <c r="H12" s="39">
+        <v>347.7</v>
+      </c>
+      <c r="I12" s="39">
+        <v>46.99</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/9b426609-bc11-4864-9624-040a9c036d97_Thi_công_cọc_khoan_nhồi__tường_vây_P8-11_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/9b426609-bc11-4864-9624-040a9c036d97_Thi_công_cọc_khoan_nhồi__tường_vây_P8-11_D800_02-04-2026.xlsx
@@ -129,7 +129,7 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">02:08
+    <t xml:space="preserve">02:00
 02/04/2026</t>
   </si>
   <si>
@@ -1315,13 +1315,13 @@
         <v>16.4</v>
       </c>
       <c r="H13" s="12">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="I13" s="12">
         <v>24.6</v>
       </c>
       <c r="J13" s="8">
-        <v>28.38</v>
+        <v>24.6</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1785,13 +1785,13 @@
         <v>16.4</v>
       </c>
       <c r="G4" s="12">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="H4" s="12">
         <v>24.6</v>
       </c>
       <c r="I4" s="8">
-        <v>28.38</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2017,13 +2017,13 @@
         <v>44.9</v>
       </c>
       <c r="G12" s="39">
-        <v>7.4</v>
+        <v>7.53</v>
       </c>
       <c r="H12" s="39">
         <v>347.7</v>
       </c>
       <c r="I12" s="39">
-        <v>46.99</v>
+        <v>46.15</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/9b426609-bc11-4864-9624-040a9c036d97_Thi_công_cọc_khoan_nhồi__tường_vây_P8-11_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/9b426609-bc11-4864-9624-040a9c036d97_Thi_công_cọc_khoan_nhồi__tường_vây_P8-11_D800_02-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">01:00
@@ -140,7 +140,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">03:01
@@ -154,7 +154,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">03:41
@@ -168,7 +168,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">04:21
@@ -182,7 +182,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">05:01
@@ -196,7 +196,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">05:41
@@ -210,9 +210,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">07:06
 02/04/2026</t>
   </si>
@@ -224,7 +221,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08:28
@@ -269,7 +266,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -352,6 +349,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -362,7 +365,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -442,6 +445,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -537,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -647,13 +655,16 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1242,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>6.3</v>
+        <v>-6.3</v>
       </c>
       <c r="H11" s="5">
         <v>0.33</v>
@@ -1274,7 +1285,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>6.3</v>
+        <v>-6.3</v>
       </c>
       <c r="G12" s="9">
         <v>-8.2</v>
@@ -1283,10 +1294,10 @@
         <v>0.32</v>
       </c>
       <c r="I12" s="9">
-        <v>14.5</v>
+        <v>1.9</v>
       </c>
       <c r="J12" s="8">
-        <v>45.79</v>
+        <v>6</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1312,16 +1323,16 @@
         <v>-8.2</v>
       </c>
       <c r="G13" s="12">
-        <v>16.4</v>
+        <v>-16.4</v>
       </c>
       <c r="H13" s="12">
         <v>1</v>
       </c>
       <c r="I13" s="12">
-        <v>24.6</v>
+        <v>8.2</v>
       </c>
       <c r="J13" s="8">
-        <v>24.6</v>
+        <v>8.2</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1344,7 +1355,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="15">
-        <v>16.4</v>
+        <v>-16.4</v>
       </c>
       <c r="G14" s="15">
         <v>-21.5</v>
@@ -1353,10 +1364,10 @@
         <v>0.65</v>
       </c>
       <c r="I14" s="15">
-        <v>37.9</v>
+        <v>5.1</v>
       </c>
       <c r="J14" s="8">
-        <v>58.31</v>
+        <v>7.85</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1487,16 +1498,16 @@
         <v>-37.3</v>
       </c>
       <c r="G18" s="28">
-        <v>39.5</v>
+        <v>-39.5</v>
       </c>
       <c r="H18" s="28">
         <v>0.65</v>
       </c>
       <c r="I18" s="28">
-        <v>76.8</v>
-      </c>
-      <c r="J18" s="8">
-        <v>118.15</v>
+        <v>2.2</v>
+      </c>
+      <c r="J18" s="21">
+        <v>3.38</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1510,16 +1521,16 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>62</v>
-      </c>
       <c r="F19" s="31">
-        <v>39.5</v>
+        <v>-39.5</v>
       </c>
       <c r="G19" s="31">
         <v>-43.7</v>
@@ -1528,10 +1539,10 @@
         <v>1.35</v>
       </c>
       <c r="I19" s="31">
-        <v>83.2</v>
-      </c>
-      <c r="J19" s="8">
-        <v>61.63</v>
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="21">
+        <v>3.11</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1539,53 +1550,53 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>65</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>66</v>
       </c>
       <c r="F20" s="34">
         <v>-43.7</v>
       </c>
       <c r="G20" s="34">
-        <v>44.9</v>
+        <v>-44.9</v>
       </c>
       <c r="H20" s="34">
         <v>1.28</v>
       </c>
       <c r="I20" s="34">
-        <v>88.6</v>
-      </c>
-      <c r="J20" s="8">
-        <v>69.04</v>
+        <v>1.2</v>
+      </c>
+      <c r="J20" s="37">
+        <v>0.94</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
+      <c r="A23" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1680,31 +1691,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1724,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>6.3</v>
+        <v>-6.3</v>
       </c>
       <c r="G2" s="5">
         <v>0.33</v>
@@ -1750,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>6.3</v>
+        <v>-6.3</v>
       </c>
       <c r="F3" s="9">
         <v>-8.2</v>
@@ -1759,10 +1770,10 @@
         <v>0.32</v>
       </c>
       <c r="H3" s="9">
-        <v>14.5</v>
+        <v>1.9</v>
       </c>
       <c r="I3" s="8">
-        <v>45.79</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1782,16 +1793,16 @@
         <v>-8.2</v>
       </c>
       <c r="F4" s="12">
-        <v>16.4</v>
+        <v>-16.4</v>
       </c>
       <c r="G4" s="12">
         <v>1</v>
       </c>
       <c r="H4" s="12">
-        <v>24.6</v>
+        <v>8.2</v>
       </c>
       <c r="I4" s="8">
-        <v>24.6</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1808,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>16.4</v>
+        <v>-16.4</v>
       </c>
       <c r="F5" s="15">
         <v>-21.5</v>
@@ -1817,10 +1828,10 @@
         <v>0.65</v>
       </c>
       <c r="H5" s="15">
-        <v>37.9</v>
+        <v>5.1</v>
       </c>
       <c r="I5" s="8">
-        <v>58.31</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1927,16 +1938,16 @@
         <v>-37.3</v>
       </c>
       <c r="F9" s="28">
-        <v>39.5</v>
+        <v>-39.5</v>
       </c>
       <c r="G9" s="28">
         <v>0.65</v>
       </c>
       <c r="H9" s="28">
-        <v>76.8</v>
-      </c>
-      <c r="I9" s="8">
-        <v>118.15</v>
+        <v>2.2</v>
+      </c>
+      <c r="I9" s="21">
+        <v>3.38</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1947,13 +1958,13 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>39.5</v>
+        <v>-39.5</v>
       </c>
       <c r="F10" s="31">
         <v>-43.7</v>
@@ -1962,10 +1973,10 @@
         <v>1.35</v>
       </c>
       <c r="H10" s="31">
-        <v>83.2</v>
-      </c>
-      <c r="I10" s="8">
-        <v>61.63</v>
+        <v>4.2</v>
+      </c>
+      <c r="I10" s="21">
+        <v>3.11</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1976,7 +1987,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1985,45 +1996,45 @@
         <v>-43.7</v>
       </c>
       <c r="F11" s="34">
-        <v>44.9</v>
+        <v>-44.9</v>
       </c>
       <c r="G11" s="34">
         <v>1.28</v>
       </c>
       <c r="H11" s="34">
-        <v>88.6</v>
-      </c>
-      <c r="I11" s="8">
-        <v>69.04</v>
+        <v>1.2</v>
+      </c>
+      <c r="I11" s="37">
+        <v>0.94</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="39" t="s">
+      <c r="A12" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="40">
         <v>10</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="40">
         <v>0</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="40">
+        <v>-44.9</v>
+      </c>
+      <c r="G12" s="40">
+        <v>7.53</v>
+      </c>
+      <c r="H12" s="40">
         <v>44.9</v>
       </c>
-      <c r="G12" s="39">
-        <v>7.53</v>
-      </c>
-      <c r="H12" s="39">
-        <v>347.7</v>
-      </c>
-      <c r="I12" s="39">
-        <v>46.15</v>
+      <c r="I12" s="40">
+        <v>5.96</v>
       </c>
     </row>
   </sheetData>
